--- a/data/trans_orig/Q57-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q57-Habitat-trans_orig.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la autopercepción de felicidad</t>
+          <t>Puntuación media de la autopercepción de felicidad (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,79</t>
+          <t>7,54; 7,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 8,1</t>
+          <t>7,82; 8,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,54</t>
+          <t>7,27; 7,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 7,93</t>
+          <t>7,71; 7,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,63</t>
+          <t>7,44; 7,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 7,99</t>
+          <t>7,81; 7,98</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 7,72</t>
+          <t>7,51; 7,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 8,65</t>
+          <t>8,16; 8,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 7,96</t>
+          <t>7,75; 7,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 7,59</t>
+          <t>7,44; 7,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 8,44</t>
+          <t>8,01; 8,45</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 7,83</t>
+          <t>7,63; 7,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,36; 8,62</t>
+          <t>8,37; 8,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -806,17 +806,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,32</t>
+          <t>7,55; 8,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 7,72</t>
+          <t>7,57; 7,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 8,43</t>
+          <t>7,77; 8,42</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 7,85</t>
+          <t>7,65; 7,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -881,22 +881,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,53</t>
+          <t>7,31; 7,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,64; 7,84</t>
+          <t>7,63; 7,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,64</t>
+          <t>7,5; 7,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 7,91</t>
+          <t>7,77; 7,91</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 7,74</t>
+          <t>7,64; 7,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 8,38</t>
+          <t>8,13; 8,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 7,5</t>
+          <t>7,39; 7,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 8,13</t>
+          <t>7,94; 8,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q57-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q57-Habitat-trans_orig.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,83</t>
+          <t>7,82</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,22 +631,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,8</t>
+          <t>7,54; 7,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 8,1</t>
+          <t>7,81; 8,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,55</t>
+          <t>7,26; 7,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 7,94</t>
+          <t>7,72; 7,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 7,98</t>
+          <t>7,8; 7,97</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,37</t>
+          <t>8,19</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>7,85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,14</t>
+          <t>8,02</t>
         </is>
       </c>
     </row>
@@ -711,32 +711,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 7,72</t>
+          <t>7,51; 7,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,16; 8,68</t>
+          <t>8,08; 8,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,52</t>
+          <t>7,32; 7,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 7,96</t>
+          <t>7,76; 7,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 7,58</t>
+          <t>7,44; 7,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 8,45</t>
+          <t>7,94; 8,09</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,5</t>
+          <t>8,48</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>8,31</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>8,39</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,37; 8,62</t>
+          <t>8,35; 8,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -806,17 +806,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,32</t>
+          <t>8,21; 8,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 7,73</t>
+          <t>7,56; 7,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 8,42</t>
+          <t>8,31; 8,48</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,83</t>
+          <t>7,81</t>
         </is>
       </c>
     </row>
@@ -871,32 +871,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 7,84</t>
+          <t>7,64; 7,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 8,05</t>
+          <t>7,81; 8,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,54</t>
+          <t>7,31; 7,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 7,82</t>
+          <t>7,6; 7,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,65</t>
+          <t>7,49; 7,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 7,91</t>
+          <t>7,74; 7,89</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,21</t>
+          <t>8,14</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>7,9</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>8,02</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,64; 7,74</t>
+          <t>7,63; 7,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 8,39</t>
+          <t>8,07; 8,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -966,17 +966,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 7,93</t>
+          <t>7,85; 7,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 7,61</t>
+          <t>7,52; 7,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,94; 8,13</t>
+          <t>7,97; 8,05</t>
         </is>
       </c>
     </row>
